--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515876</v>
+        <v>121515873</v>
       </c>
       <c r="B2" t="n">
         <v>57354</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594068</v>
+        <v>594067</v>
       </c>
       <c r="R2" t="n">
-        <v>7183717</v>
+        <v>7183732</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515873</v>
+        <v>121515875</v>
       </c>
       <c r="B4" t="n">
         <v>57354</v>
@@ -940,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594067</v>
+        <v>594065</v>
       </c>
       <c r="R4" t="n">
-        <v>7183732</v>
+        <v>7183731</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515870</v>
+        <v>121515869</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594087</v>
+        <v>594086</v>
       </c>
       <c r="R6" t="n">
         <v>7183741</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515869</v>
+        <v>121515870</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594086</v>
+        <v>594087</v>
       </c>
       <c r="R7" t="n">
         <v>7183741</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515875</v>
+        <v>121515876</v>
       </c>
       <c r="B8" t="n">
         <v>57354</v>
@@ -1398,7 +1398,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594065</v>
+        <v>594068</v>
       </c>
       <c r="R8" t="n">
-        <v>7183731</v>
+        <v>7183717</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515873</v>
+        <v>121515876</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594067</v>
+        <v>594068</v>
       </c>
       <c r="R2" t="n">
-        <v>7183732</v>
+        <v>7183717</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515868</v>
+        <v>121515870</v>
       </c>
       <c r="B3" t="n">
-        <v>77544</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594083</v>
+        <v>594087</v>
       </c>
       <c r="R3" t="n">
         <v>7183741</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515875</v>
+        <v>121515868</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>77545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594065</v>
+        <v>594083</v>
       </c>
       <c r="R4" t="n">
-        <v>7183731</v>
+        <v>7183741</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1019,7 @@
         <v>121515872</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515869</v>
+        <v>121515873</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594086</v>
+        <v>594067</v>
       </c>
       <c r="R6" t="n">
-        <v>7183741</v>
+        <v>7183732</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515870</v>
+        <v>121515875</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594087</v>
+        <v>594065</v>
       </c>
       <c r="R7" t="n">
-        <v>7183741</v>
+        <v>7183731</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515876</v>
+        <v>121515869</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594068</v>
+        <v>594086</v>
       </c>
       <c r="R8" t="n">
-        <v>7183717</v>
+        <v>7183741</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121515876</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>121515870</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515868</v>
+        <v>121515872</v>
       </c>
       <c r="B4" t="n">
-        <v>77545</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594083</v>
+        <v>594075</v>
       </c>
       <c r="R4" t="n">
-        <v>7183741</v>
+        <v>7183737</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515872</v>
+        <v>121515869</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594075</v>
+        <v>594086</v>
       </c>
       <c r="R5" t="n">
-        <v>7183737</v>
+        <v>7183741</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515873</v>
+        <v>121515868</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>77546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594067</v>
+        <v>594083</v>
       </c>
       <c r="R6" t="n">
-        <v>7183732</v>
+        <v>7183741</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1248,7 @@
         <v>121515875</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515869</v>
+        <v>121515873</v>
       </c>
       <c r="B8" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594086</v>
+        <v>594067</v>
       </c>
       <c r="R8" t="n">
-        <v>7183741</v>
+        <v>7183732</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515876</v>
+        <v>121515870</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594068</v>
+        <v>594087</v>
       </c>
       <c r="R2" t="n">
-        <v>7183717</v>
+        <v>7183741</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515870</v>
+        <v>121515869</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,7 +827,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594087</v>
+        <v>594086</v>
       </c>
       <c r="R3" t="n">
         <v>7183741</v>
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515872</v>
+        <v>121515873</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -940,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594075</v>
+        <v>594067</v>
       </c>
       <c r="R4" t="n">
-        <v>7183737</v>
+        <v>7183732</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515869</v>
+        <v>121515876</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594086</v>
+        <v>594068</v>
       </c>
       <c r="R5" t="n">
-        <v>7183741</v>
+        <v>7183717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515868</v>
+        <v>121515875</v>
       </c>
       <c r="B6" t="n">
-        <v>77546</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594083</v>
+        <v>594065</v>
       </c>
       <c r="R6" t="n">
-        <v>7183741</v>
+        <v>7183731</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515875</v>
+        <v>121515872</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1290,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594065</v>
+        <v>594075</v>
       </c>
       <c r="R7" t="n">
-        <v>7183731</v>
+        <v>7183737</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515873</v>
+        <v>121515868</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>77546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594067</v>
+        <v>594083</v>
       </c>
       <c r="R8" t="n">
-        <v>7183732</v>
+        <v>7183741</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515870</v>
+        <v>121515868</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>77546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594087</v>
+        <v>594083</v>
       </c>
       <c r="R2" t="n">
         <v>7183741</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515869</v>
+        <v>121515876</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594086</v>
+        <v>594068</v>
       </c>
       <c r="R3" t="n">
-        <v>7183741</v>
+        <v>7183717</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515873</v>
+        <v>121515869</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594067</v>
+        <v>594086</v>
       </c>
       <c r="R4" t="n">
-        <v>7183732</v>
+        <v>7183741</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515876</v>
+        <v>121515872</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1052,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594068</v>
+        <v>594075</v>
       </c>
       <c r="R5" t="n">
-        <v>7183717</v>
+        <v>7183737</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515875</v>
+        <v>121515873</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1169,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594065</v>
+        <v>594067</v>
       </c>
       <c r="R6" t="n">
-        <v>7183731</v>
+        <v>7183732</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515872</v>
+        <v>121515875</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594075</v>
+        <v>594065</v>
       </c>
       <c r="R7" t="n">
-        <v>7183737</v>
+        <v>7183731</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515868</v>
+        <v>121515870</v>
       </c>
       <c r="B8" t="n">
-        <v>77546</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594083</v>
+        <v>594087</v>
       </c>
       <c r="R8" t="n">
         <v>7183741</v>

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515868</v>
+        <v>121515873</v>
       </c>
       <c r="B2" t="n">
-        <v>77546</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594083</v>
+        <v>594067</v>
       </c>
       <c r="R2" t="n">
-        <v>7183741</v>
+        <v>7183732</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515876</v>
+        <v>121515870</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594068</v>
+        <v>594087</v>
       </c>
       <c r="R3" t="n">
-        <v>7183717</v>
+        <v>7183741</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515872</v>
+        <v>121515875</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594075</v>
+        <v>594065</v>
       </c>
       <c r="R5" t="n">
-        <v>7183737</v>
+        <v>7183731</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515873</v>
+        <v>121515876</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594067</v>
+        <v>594068</v>
       </c>
       <c r="R6" t="n">
-        <v>7183732</v>
+        <v>7183717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515875</v>
+        <v>121515868</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>77546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594065</v>
+        <v>594083</v>
       </c>
       <c r="R7" t="n">
-        <v>7183731</v>
+        <v>7183741</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515870</v>
+        <v>121515872</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594087</v>
+        <v>594075</v>
       </c>
       <c r="R8" t="n">
-        <v>7183741</v>
+        <v>7183737</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515875</v>
+        <v>121515870</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594065</v>
+        <v>594087</v>
       </c>
       <c r="R3" t="n">
-        <v>7183731</v>
+        <v>7183741</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515870</v>
+        <v>121515876</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594087</v>
+        <v>594068</v>
       </c>
       <c r="R4" t="n">
-        <v>7183741</v>
+        <v>7183717</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515869</v>
+        <v>121515872</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594086</v>
+        <v>594075</v>
       </c>
       <c r="R5" t="n">
-        <v>7183741</v>
+        <v>7183737</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515873</v>
+        <v>121515869</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594067</v>
+        <v>594086</v>
       </c>
       <c r="R6" t="n">
-        <v>7183732</v>
+        <v>7183741</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515872</v>
+        <v>121515873</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1281,7 +1281,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594075</v>
+        <v>594067</v>
       </c>
       <c r="R7" t="n">
-        <v>7183737</v>
+        <v>7183732</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515876</v>
+        <v>121515875</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1398,7 +1398,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594068</v>
+        <v>594065</v>
       </c>
       <c r="R8" t="n">
-        <v>7183717</v>
+        <v>7183731</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515868</v>
+        <v>121515870</v>
       </c>
       <c r="B2" t="n">
-        <v>77553</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594083</v>
+        <v>594087</v>
       </c>
       <c r="R2" t="n">
         <v>7183741</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515870</v>
+        <v>121515869</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594087</v>
+        <v>594086</v>
       </c>
       <c r="R3" t="n">
         <v>7183741</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515876</v>
+        <v>121515868</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>77553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594068</v>
+        <v>594083</v>
       </c>
       <c r="R4" t="n">
-        <v>7183717</v>
+        <v>7183741</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515872</v>
+        <v>121515875</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594075</v>
+        <v>594065</v>
       </c>
       <c r="R5" t="n">
-        <v>7183737</v>
+        <v>7183731</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515869</v>
+        <v>121515876</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594086</v>
+        <v>594068</v>
       </c>
       <c r="R6" t="n">
-        <v>7183741</v>
+        <v>7183717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1362,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515875</v>
+        <v>121515872</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594065</v>
+        <v>594075</v>
       </c>
       <c r="R8" t="n">
-        <v>7183731</v>
+        <v>7183737</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515870</v>
+        <v>121515872</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594087</v>
+        <v>594075</v>
       </c>
       <c r="R2" t="n">
-        <v>7183741</v>
+        <v>7183737</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515869</v>
+        <v>121515868</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>77553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +832,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594086</v>
+        <v>594083</v>
       </c>
       <c r="R3" t="n">
         <v>7183741</v>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515868</v>
+        <v>121515869</v>
       </c>
       <c r="B4" t="n">
-        <v>77553</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,7 +944,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594083</v>
+        <v>594086</v>
       </c>
       <c r="R4" t="n">
         <v>7183741</v>
@@ -1011,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515875</v>
+        <v>121515876</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1047,7 +1052,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594065</v>
+        <v>594068</v>
       </c>
       <c r="R5" t="n">
-        <v>7183731</v>
+        <v>7183717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515876</v>
+        <v>121515875</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1164,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594068</v>
+        <v>594065</v>
       </c>
       <c r="R6" t="n">
-        <v>7183717</v>
+        <v>7183731</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515872</v>
+        <v>121515870</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594075</v>
+        <v>594087</v>
       </c>
       <c r="R8" t="n">
-        <v>7183737</v>
+        <v>7183741</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515868</v>
+        <v>121515870</v>
       </c>
       <c r="B3" t="n">
-        <v>77553</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594083</v>
+        <v>594087</v>
       </c>
       <c r="R3" t="n">
         <v>7183741</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515869</v>
+        <v>121515876</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594086</v>
+        <v>594068</v>
       </c>
       <c r="R4" t="n">
-        <v>7183741</v>
+        <v>7183717</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515876</v>
+        <v>121515869</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594068</v>
+        <v>594086</v>
       </c>
       <c r="R5" t="n">
-        <v>7183717</v>
+        <v>7183741</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515870</v>
+        <v>121515868</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>77553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594087</v>
+        <v>594083</v>
       </c>
       <c r="R8" t="n">
         <v>7183741</v>

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515872</v>
+        <v>121515876</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594075</v>
+        <v>594068</v>
       </c>
       <c r="R2" t="n">
-        <v>7183737</v>
+        <v>7183717</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515870</v>
+        <v>121515869</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594087</v>
+        <v>594086</v>
       </c>
       <c r="R3" t="n">
         <v>7183741</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515876</v>
+        <v>121515868</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>77553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594068</v>
+        <v>594083</v>
       </c>
       <c r="R4" t="n">
-        <v>7183717</v>
+        <v>7183741</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515869</v>
+        <v>121515870</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,7 +1056,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594086</v>
+        <v>594087</v>
       </c>
       <c r="R5" t="n">
         <v>7183741</v>
@@ -1133,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515875</v>
+        <v>121515872</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1178,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594065</v>
+        <v>594075</v>
       </c>
       <c r="R6" t="n">
-        <v>7183731</v>
+        <v>7183737</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121515868</v>
+        <v>121515875</v>
       </c>
       <c r="B8" t="n">
-        <v>77553</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594083</v>
+        <v>594065</v>
       </c>
       <c r="R8" t="n">
-        <v>7183741</v>
+        <v>7183731</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28867-2024 artfynd.xlsx
+++ b/artfynd/A 28867-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121515876</v>
+        <v>121515870</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594068</v>
+        <v>594087</v>
       </c>
       <c r="R2" t="n">
-        <v>7183717</v>
+        <v>7183741</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515869</v>
+        <v>121515872</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594086</v>
+        <v>594075</v>
       </c>
       <c r="R3" t="n">
-        <v>7183741</v>
+        <v>7183737</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121515868</v>
+        <v>121515873</v>
       </c>
       <c r="B4" t="n">
-        <v>77553</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594083</v>
+        <v>594067</v>
       </c>
       <c r="R4" t="n">
-        <v>7183741</v>
+        <v>7183732</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121515870</v>
+        <v>121515875</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594087</v>
+        <v>594065</v>
       </c>
       <c r="R5" t="n">
-        <v>7183741</v>
+        <v>7183731</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121515872</v>
+        <v>121515876</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1149,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594075</v>
+        <v>594068</v>
       </c>
       <c r="R6" t="n">
-        <v>7183737</v>
+        <v>7183717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121515873</v>
+        <v>121515868</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,39 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594067</v>
+        <v>594083</v>
       </c>
       <c r="R7" t="n">
-        <v>7183732</v>
+        <v>7183741</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,123 +1334,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>121515875</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>594065</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7183731</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
